--- a/draw_pics/theoritical_raw_data.xlsx
+++ b/draw_pics/theoritical_raw_data.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10102"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1ECBA7-C14B-BF48-B413-D3BD371701B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243B2C4C-5B3A-A746-AEAD-72C0E71748BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17280" yWindow="680" windowWidth="17300" windowHeight="20200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="820" windowWidth="17300" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -360,12 +360,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="B1">
         <v>0</v>
@@ -373,48 +373,119 @@
       <c r="C1">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2">
-        <v>22.2</v>
+        <v>19.18</v>
       </c>
       <c r="B2">
-        <v>3.28</v>
+        <v>2.6</v>
       </c>
       <c r="C2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D2">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>22.16</v>
+      </c>
+      <c r="B3">
+        <v>4.2</v>
+      </c>
+      <c r="C3">
+        <v>3.8</v>
+      </c>
+      <c r="D3">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>26.05</v>
+      </c>
+      <c r="B4">
+        <v>5.9</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>30.08</v>
+      </c>
+      <c r="B5">
+        <v>7.1</v>
+      </c>
+      <c r="C5">
+        <v>7.3</v>
+      </c>
+      <c r="D5">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>36.24</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>7.9</v>
+      </c>
+      <c r="D6">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>39.26</v>
+      </c>
+      <c r="B7">
+        <v>7.5</v>
+      </c>
+      <c r="C7">
+        <v>7.3</v>
+      </c>
+      <c r="D7">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>42.92</v>
+      </c>
+      <c r="B8">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="C8">
+        <v>8.1</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>11.29</v>
+      </c>
+      <c r="B9">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>26.1</v>
-      </c>
-      <c r="B3">
-        <v>4.54</v>
-      </c>
-      <c r="C3">
+      <c r="C9">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>30.1</v>
-      </c>
-      <c r="B4">
-        <v>6.08</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
+      <c r="D9">
         <v>0</v>
       </c>
     </row>
